--- a/ig/DM-FEVRIER-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-FEVRIER-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:51:23+00:00</t>
+    <t>2025-02-28T10:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-FEVRIER-2025/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/ASS_12_CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.json</t>
+    <t>https://mos.esante.gouv.fr/NOS/ASS_A12_CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.json</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>ASS_12_CorresMediaTypeCDANonStructure_XdsFormatCode_CISIS</t>
+    <t>ASS_A12_CorresMediaTypeCDANonStructure_XdsFormatCode_CISIS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>ASS_12_CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS</t>
+    <t>ASS_A12_CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:48:02+00:00</t>
+    <t>2025-02-28T14:32:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
